--- a/public/sap-reporting/expansion-150-downloads/EXT-PM08-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-PM08-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Re7ddbbb518964995"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R1d8fc30afa234d0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R0a51053dad6e4459"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rcb80350544fb4549"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R9b7b964ed10c4b9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R5d6d8fa3fb954f56"/>
   </x:sheets>
 </x:workbook>
 </file>
